--- a/reports/pdf_rolling5_20260819.xlsx
+++ b/reports/pdf_rolling5_20260819.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,10 +57,6 @@
     <font>
       <b val="1"/>
       <color rgb="000070C0"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
     </font>
     <font>
       <b val="1"/>
@@ -170,8 +166,8 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -540,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -566,14 +562,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-08-11 ~ 2026-08-19  (최근 5거래일)  ·  캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-08-11 ~ 2026-08-19  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,778억   ·   현금 273억(5.5%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 14종목  /  매도 14종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,778억   ·   현금 273억(5.7%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 17종목  /  매도 17종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -669,11 +665,11 @@
         <v>244</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2857945160</v>
+        <v>2707794880</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.61%</t>
+          <t>0.00%→0.59%</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
@@ -687,19 +683,19 @@
         </is>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-193</v>
+        <v>-337</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1994873090</v>
+        <v>-3465701260</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>1.42%→1.00%</t>
+          <t>1.42%→0.70%</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>645→452</t>
+          <t>645→308</t>
         </is>
       </c>
     </row>
@@ -713,11 +709,11 @@
         <v>126</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1329950160</v>
+        <v>1389088260</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>1.65%→1.80%</t>
+          <t>1.65%→1.92%</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -727,287 +723,287 @@
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>씨어스  (편출)</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-36</v>
+        <v>-62</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-929313000</v>
+        <v>-962230080</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.00%</t>
+          <t>0.92%→0.69%</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>36→0</t>
+          <t>263→201</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>하나머티리얼즈</t>
+          <t>감성코퍼레이션</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>4195676100</v>
+        <v>460828690</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>1.02%→1.88%</t>
+          <t>0.46%→0.50%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>75→144</t>
+          <t>440→553</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>씨어스  (편출)</t>
         </is>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-35</v>
+        <v>-36</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-2391077500</v>
+        <v>-929313000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>0.98%→0.53%</t>
+          <t>0.20%→0.00%</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>71→36</t>
+          <t>36→0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>한텍</t>
+          <t>하나머티리얼즈</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1461660200</v>
+        <v>4066135500</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>0.29%→0.62%</t>
+          <t>1.02%→1.86%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>47→96</t>
+          <t>75→144</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-33</v>
+        <v>-35</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-3741345300</v>
+        <v>-2493291500</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>5.65%→4.49%</t>
+          <t>0.98%→0.56%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>217→184</t>
+          <t>71→36</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>957943350</v>
+        <v>861632730</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>1.22%→1.44%</t>
+          <t>1.01%→1.09%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>233→272</t>
+          <t>318→385</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-29</v>
+        <v>-33</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-978490450</v>
+        <v>-3817067100</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.80%→0.60%</t>
+          <t>5.65%→4.68%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>112→83</t>
+          <t>217→184</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>한텍</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>433908860</v>
+        <v>1323671300</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>1.01%→1.05%</t>
+          <t>0.29%→0.57%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>318→349</t>
+          <t>47→96</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-27</v>
+        <v>-33</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-2368340100</v>
+        <v>-1349224800</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>2.77%→1.98%</t>
+          <t>1.50%→1.48%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>132→105</t>
+          <t>198→165</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>한국피아이엠  (신규)</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>2195932200</v>
+        <v>929469450</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.47%</t>
+          <t>1.22%→1.42%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>0→29</t>
+          <t>233→272</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>노바렉스  (편출)</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-26</v>
+        <v>-29</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-455582400</v>
+        <v>-916484100</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>0.10%→0.00%</t>
+          <t>0.80%→0.58%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>26→0</t>
+          <t>112→83</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>큐리언트</t>
+          <t>한국피아이엠  (신규)</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>480614400</v>
+        <v>1845067000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>1.24%→1.27%</t>
+          <t>0.00%→0.41%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>204→222</t>
+          <t>0→29</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-25</v>
+        <v>-27</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-2899540000</v>
+        <v>-2247247800</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>3.96%→3.57%</t>
+          <t>2.77%→1.92%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>168→143</t>
+          <t>132→105</t>
         </is>
       </c>
     </row>
@@ -1018,40 +1014,40 @@
         </is>
       </c>
       <c r="B14" s="11" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1484397600</v>
+        <v>3041388000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>0.55%→0.93%</t>
+          <t>0.55%→1.24%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>23→35</t>
+          <t>23→50</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>노바렉스  (편출)</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-19</v>
+        <v>-26</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1894505200</v>
+        <v>-455582400</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>1.11%→0.66%</t>
+          <t>0.10%→0.00%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>50→31</t>
+          <t>26→0</t>
         </is>
       </c>
     </row>
@@ -1062,864 +1058,2032 @@
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>467472600</v>
+        <v>963732000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>0.70%→0.89%</t>
+          <t>0.70%→1.04%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>94→106</t>
+          <t>94→118</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-15</v>
+        <v>-25</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-960603000</v>
+        <v>-2912577500</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.81%→0.55%</t>
+          <t>3.96%→3.66%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>55→40</t>
+          <t>168→143</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>큐리언트</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>474043500</v>
+        <v>462779100</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>1.35%→1.48%</t>
+          <t>1.24%→1.25%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>122→131</t>
+          <t>204→222</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-8</v>
+        <v>-24</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-320409600</v>
+        <v>-927435600</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.68%→0.64%</t>
+          <t>0.82%→0.63%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>82→74</t>
+          <t>98→74</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>2169440000</v>
+        <v>955700900</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>2.34%→3.15%</t>
+          <t>1.38%→1.64%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>46→54</t>
+          <t>116→133</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-8</v>
+        <v>-20</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-950381600</v>
+        <v>-713412000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>2.07%→1.76%</t>
+          <t>0.68%→0.49%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>77→69</t>
+          <t>82→62</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2292514000</v>
+        <v>902925100</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>6.25%→6.13%</t>
+          <t>0.65%→0.94%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>80→87</t>
+          <t>41→52</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-7</v>
+        <v>-19</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-532242900</v>
+        <v>-1722097300</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.35%→0.25%</t>
+          <t>1.11%→0.62%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>22→15</t>
+          <t>50→31</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
+          <t>이엔에프테크놀로지</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>458554950</v>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>1.35%→1.47%</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>122→131</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>디앤디파마텍</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>-15</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>-904281000</v>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>0.81%→0.53%</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>55→40</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>2244536000</v>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>2.34%→3.33%</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>46→54</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v>-876954400</v>
+      </c>
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>2.07%→1.66%</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>77→69</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>2175698000</v>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>6.25%→5.94%</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>80→87</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>-486246600</v>
+      </c>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>0.35%→0.23%</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>22→15</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
           <t>제주반도체</t>
         </is>
       </c>
-      <c r="B19" s="11" t="n">
+      <c r="B22" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C19" s="11" t="n">
-        <v>425022500</v>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>3.27%→3.13%</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="C22" s="11" t="n">
+        <v>395297000</v>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>3.27%→2.97%</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>166→171</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="G22" s="14" t="inlineStr">
         <is>
           <t>파마리서치</t>
         </is>
       </c>
-      <c r="H19" s="15" t="n">
+      <c r="H22" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I19" s="15" t="n">
-        <v>-1245342000</v>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>2.95%→2.59%</t>
-        </is>
-      </c>
-      <c r="K19" s="13" t="inlineStr">
+      <c r="I22" s="15" t="n">
+        <v>-1229697000</v>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>2.95%→2.61%</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
         <is>
           <t>32→29</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,023억   ·   현금 20억(0.5%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="n"/>
-      <c r="J21" s="4" t="n"/>
-      <c r="K21" s="4" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>변화 없음 (구성종목 동일)</t>
-        </is>
-      </c>
-    </row>
     <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="n"/>
-      <c r="C24" s="19" t="n"/>
-      <c r="D24" s="19" t="n"/>
-      <c r="E24" s="19" t="n"/>
-      <c r="F24" s="19" t="n"/>
-      <c r="G24" s="19" t="n"/>
-      <c r="H24" s="19" t="n"/>
-      <c r="I24" s="19" t="n"/>
-      <c r="J24" s="19" t="n"/>
-      <c r="K24" s="19" t="n"/>
-    </row>
-    <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="n"/>
-      <c r="C26" s="19" t="n"/>
-      <c r="D26" s="19" t="n"/>
-      <c r="E26" s="19" t="n"/>
-      <c r="F26" s="19" t="n"/>
-      <c r="G26" s="19" t="n"/>
-      <c r="H26" s="19" t="n"/>
-      <c r="I26" s="19" t="n"/>
-      <c r="J26" s="19" t="n"/>
-      <c r="K26" s="19" t="n"/>
-    </row>
-    <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 295억   ·   현금 15억(4.8%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 10종목  /  매도 10종목</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="n"/>
-      <c r="J28" s="4" t="n"/>
-      <c r="K28" s="4" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,023억   ·   현금 11억(0.3%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 1종목  /  매도 2종목</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="4" t="n"/>
+      <c r="K24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H29" s="8" t="n"/>
-      <c r="I29" s="8" t="n"/>
-      <c r="J29" s="8" t="n"/>
-      <c r="K29" s="8" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="H25" s="8" t="n"/>
+      <c r="I25" s="8" t="n"/>
+      <c r="J25" s="8" t="n"/>
+      <c r="K25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr">
+      <c r="H26" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I30" s="9" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J30" s="9" t="inlineStr">
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K30" s="9" t="inlineStr">
+      <c r="K26" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>인제니아테라퓨틱스(Reg.S)  (신규)</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>424</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>4027457280</v>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.05%</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>0→424</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>-123</v>
+      </c>
+      <c r="I27" s="15" t="n">
+        <v>-1457992800</v>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>1.06%→0.69%</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>345→222</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="n"/>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>녹십자</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I28" s="15" t="n">
+        <v>-321552000</v>
+      </c>
+      <c r="J28" s="16" t="inlineStr">
+        <is>
+          <t>3.04%→2.99%</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>183→178</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="19" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,774억   ·   현금 81억(3.0%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 8종목  /  매도 12종목</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="n"/>
+      <c r="J30" s="4" t="n"/>
+      <c r="K30" s="4" t="n"/>
+    </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>코스맥스엔비티</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="n">
-        <v>105</v>
-      </c>
-      <c r="C31" s="11" t="n">
-        <v>75810000</v>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>0.04%→0.31%</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>17→122</t>
-        </is>
-      </c>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>더블유씨피</t>
-        </is>
-      </c>
-      <c r="H31" s="15" t="n">
-        <v>-194</v>
-      </c>
-      <c r="I31" s="15" t="n">
-        <v>-137414080</v>
-      </c>
-      <c r="J31" s="16" t="inlineStr">
-        <is>
-          <t>7.97%→7.50%</t>
-        </is>
-      </c>
-      <c r="K31" s="13" t="inlineStr">
-        <is>
-          <t>3,246→3,052</t>
-        </is>
-      </c>
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="n"/>
+      <c r="I31" s="8" t="n"/>
+      <c r="J31" s="8" t="n"/>
+      <c r="K31" s="8" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>한선엔지니어링</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="n">
-        <v>74</v>
-      </c>
-      <c r="C32" s="11" t="n">
-        <v>68894000</v>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>1.43%→1.67%</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>442→516</t>
-        </is>
-      </c>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>새로닉스</t>
-        </is>
-      </c>
-      <c r="H32" s="15" t="n">
-        <v>-43</v>
-      </c>
-      <c r="I32" s="15" t="n">
-        <v>-36732320</v>
-      </c>
-      <c r="J32" s="16" t="inlineStr">
-        <is>
-          <t>2.81%→2.69%</t>
-        </is>
-      </c>
-      <c r="K32" s="13" t="inlineStr">
-        <is>
-          <t>950→907</t>
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>에프앤가이드</t>
+          <t>PS일렉트로닉스  (신규)</t>
         </is>
       </c>
       <c r="B33" s="11" t="n">
-        <v>34</v>
+        <v>116</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>48605040</v>
+        <v>804848600</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>3.20%→3.37%</t>
+          <t>0.00%→0.30%</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>646→680</t>
+          <t>0→116</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>덕산하이메탈</t>
         </is>
       </c>
       <c r="H33" s="15" t="n">
-        <v>-38</v>
+        <v>-275</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-52792640</v>
+        <v>-1949568500</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>1.55%→1.37%</t>
+          <t>1.30%→0.59%</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
         <is>
-          <t>322→284</t>
+          <t>499→224</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>노바렉스</t>
+          <t>미래에셋벤처투자</t>
         </is>
       </c>
       <c r="B34" s="11" t="n">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>32090240</v>
+        <v>1090162180</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>0.08%→0.20%</t>
+          <t>0.55%→0.96%</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>22→51</t>
+          <t>127→221</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>미코</t>
         </is>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-30</v>
+        <v>-171</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-60306000</v>
+        <v>-2104886880</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>2.77%→2.56%</t>
+          <t>2.33%→1.61%</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
         <is>
-          <t>397→367</t>
+          <t>521→350</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="B35" s="11" t="n">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>116348400</v>
+        <v>5357988000</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>2.65%→3.06%</t>
+          <t>1.43%→3.45%</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>138→159</t>
+          <t>50→119</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="H35" s="15" t="n">
-        <v>-27</v>
+        <v>-145</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-49145400</v>
+        <v>-3779243750</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>6.43%→6.27%</t>
+          <t>2.41%→1.49%</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>1,020→993</t>
+          <t>298→153</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="B36" s="11" t="n">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>39314800</v>
+        <v>3706013600</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>7.27%→7.42%</t>
+          <t>1.61%→2.79%</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>747→761</t>
+          <t>69→137</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>네패스</t>
         </is>
       </c>
       <c r="H36" s="15" t="n">
-        <v>-18</v>
+        <v>-130</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-50000400</v>
+        <v>-1739476700</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>2.59%→2.42%</t>
+          <t>1.13%→0.60%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
         <is>
-          <t>269→251</t>
+          <t>250→120</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>오킨스전자</t>
         </is>
       </c>
       <c r="B37" s="11" t="n">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>74350800</v>
+        <v>587998200</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>2.06%→2.32%</t>
+          <t>0.19%→0.45%</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>72→81</t>
+          <t>50→97</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
-        <v>-14</v>
+        <v>-119</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-32877600</v>
+        <v>-2939020350</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>2.61%→2.50%</t>
+          <t>1.84%→1.13%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>321→307</t>
+          <t>241→122</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>한국피아이엠  (신규)</t>
         </is>
       </c>
       <c r="B38" s="11" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>46648800</v>
+        <v>1447347000</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>3.29%→3.45%</t>
+          <t>0.00%→0.54%</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>183→192</t>
+          <t>0→33</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>씨어스  (편출)</t>
         </is>
       </c>
       <c r="H38" s="15" t="n">
-        <v>-13</v>
+        <v>-70</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-39470600</v>
+        <v>-1245667500</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>0.73%→0.59%</t>
+          <t>0.46%→0.00%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>69→56</t>
+          <t>70→0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>티에스이  (신규)</t>
         </is>
       </c>
       <c r="B39" s="11" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>61149600</v>
+        <v>2901165000</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>2.90%→3.11%</t>
+          <t>0.00%→1.08%</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>82→88</t>
+          <t>0→15</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>티씨케이</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="H39" s="15" t="n">
-        <v>-9</v>
+        <v>-34</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-166896000</v>
+        <v>-1317639400</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>2.83%→2.25%</t>
+          <t>5.26%→4.94%</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
         <is>
-          <t>44→35</t>
+          <t>375→341</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
+          <t>로보티즈</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>2808414000</v>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>1.64%→2.92%</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>25→39</t>
+        </is>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>메쥬</t>
+        </is>
+      </c>
+      <c r="H40" s="15" t="n">
+        <v>-24</v>
+      </c>
+      <c r="I40" s="15" t="n">
+        <v>-204483600</v>
+      </c>
+      <c r="J40" s="16" t="inlineStr">
+        <is>
+          <t>0.36%→0.25%</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="inlineStr">
+        <is>
+          <t>101→77</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="17" t="n"/>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>케어젠  (편출)</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="n">
+        <v>-24</v>
+      </c>
+      <c r="I41" s="15" t="n">
+        <v>-1207920000</v>
+      </c>
+      <c r="J41" s="16" t="inlineStr">
+        <is>
+          <t>0.45%→0.00%</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="inlineStr">
+        <is>
+          <t>24→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="17" t="n"/>
+      <c r="B42" s="17" t="n"/>
+      <c r="C42" s="17" t="n"/>
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="17" t="n"/>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H42" s="15" t="n">
+        <v>-23</v>
+      </c>
+      <c r="I42" s="15" t="n">
+        <v>-1847182900</v>
+      </c>
+      <c r="J42" s="16" t="inlineStr">
+        <is>
+          <t>1.95%→1.41%</t>
+        </is>
+      </c>
+      <c r="K42" s="13" t="inlineStr">
+        <is>
+          <t>70→47</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="17" t="n"/>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>선익시스템</t>
+        </is>
+      </c>
+      <c r="H43" s="15" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I43" s="15" t="n">
+        <v>-957708000</v>
+      </c>
+      <c r="J43" s="16" t="inlineStr">
+        <is>
+          <t>1.87%→1.43%</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="inlineStr">
+        <is>
+          <t>100→80</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="17" t="n"/>
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="H44" s="15" t="n">
+        <v>-18</v>
+      </c>
+      <c r="I44" s="15" t="n">
+        <v>-2320500600</v>
+      </c>
+      <c r="J44" s="16" t="inlineStr">
+        <is>
+          <t>4.73%→5.06%</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="inlineStr">
+        <is>
+          <t>123→105</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="19" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,346억   ·   현금 50억(2.2%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 4종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="n"/>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="4" t="n"/>
+      <c r="J46" s="4" t="n"/>
+      <c r="K46" s="4" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="6" t="n"/>
+      <c r="E47" s="6" t="n"/>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="n"/>
+      <c r="I47" s="8" t="n"/>
+      <c r="J47" s="8" t="n"/>
+      <c r="K47" s="8" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K48" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>셀트리온제약</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n">
+        <v>233</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>3309555300</v>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>2.48%→4.08%</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>400→633</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>일동제약  (편출)</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>-216</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <v>-1163529360</v>
+      </c>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>0.47%→0.00%</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>216→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>154</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>10206273000</v>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>8.29%→13.63%</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>299→453</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>-120</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <v>-12122640000</v>
+      </c>
+      <c r="J50" s="16" t="inlineStr">
+        <is>
+          <t>17.09%→10.82%</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
+        <is>
+          <t>356→236</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>유한양행</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="n">
+        <v>84</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>2266689600</v>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>2.27%→3.49%</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>201→285</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>-62</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>-2238417000</v>
+      </c>
+      <c r="J51" s="16" t="inlineStr">
+        <is>
+          <t>8.27%→6.11%</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="inlineStr">
+        <is>
+          <t>435→373</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>네이처셀</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>30645600</v>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>0.13%→0.16%</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>42→46</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="H52" s="15" t="n">
+        <v>-53</v>
+      </c>
+      <c r="I52" s="15" t="n">
+        <v>-1180431900</v>
+      </c>
+      <c r="J52" s="16" t="inlineStr">
+        <is>
+          <t>1.97%→1.53%</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="inlineStr">
+        <is>
+          <t>204→151</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="19" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 295억   ·   현금 15억(4.8%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 10종목  /  매도 10종목</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="4" t="n"/>
+      <c r="F54" s="4" t="n"/>
+      <c r="G54" s="4" t="n"/>
+      <c r="H54" s="4" t="n"/>
+      <c r="I54" s="4" t="n"/>
+      <c r="J54" s="4" t="n"/>
+      <c r="K54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="6" t="n"/>
+      <c r="D55" s="6" t="n"/>
+      <c r="E55" s="6" t="n"/>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="n"/>
+      <c r="I55" s="8" t="n"/>
+      <c r="J55" s="8" t="n"/>
+      <c r="K55" s="8" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H56" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K56" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>코스맥스엔비티</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="n">
+        <v>105</v>
+      </c>
+      <c r="C57" s="11" t="n">
+        <v>75810000</v>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>0.04%→0.31%</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>17→122</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>더블유씨피</t>
+        </is>
+      </c>
+      <c r="H57" s="15" t="n">
+        <v>-194</v>
+      </c>
+      <c r="I57" s="15" t="n">
+        <v>-137414080</v>
+      </c>
+      <c r="J57" s="16" t="inlineStr">
+        <is>
+          <t>7.97%→7.50%</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="inlineStr">
+        <is>
+          <t>3,246→3,052</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>한선엔지니어링</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="C58" s="11" t="n">
+        <v>68894000</v>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>1.43%→1.67%</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>442→516</t>
+        </is>
+      </c>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>새로닉스</t>
+        </is>
+      </c>
+      <c r="H58" s="15" t="n">
+        <v>-43</v>
+      </c>
+      <c r="I58" s="15" t="n">
+        <v>-36732320</v>
+      </c>
+      <c r="J58" s="16" t="inlineStr">
+        <is>
+          <t>2.81%→2.69%</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="inlineStr">
+        <is>
+          <t>950→907</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>에프앤가이드</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="C59" s="11" t="n">
+        <v>48605040</v>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>3.20%→3.37%</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>646→680</t>
+        </is>
+      </c>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>상신이디피</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="n">
+        <v>-38</v>
+      </c>
+      <c r="I59" s="15" t="n">
+        <v>-52792640</v>
+      </c>
+      <c r="J59" s="16" t="inlineStr">
+        <is>
+          <t>1.55%→1.37%</t>
+        </is>
+      </c>
+      <c r="K59" s="13" t="inlineStr">
+        <is>
+          <t>322→284</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>노바렉스</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="C60" s="11" t="n">
+        <v>32090240</v>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>0.08%→0.20%</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>22→51</t>
+        </is>
+      </c>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>스피어</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="I60" s="15" t="n">
+        <v>-60306000</v>
+      </c>
+      <c r="J60" s="16" t="inlineStr">
+        <is>
+          <t>2.77%→2.56%</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="inlineStr">
+        <is>
+          <t>397→367</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="C61" s="11" t="n">
+        <v>116348400</v>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>2.65%→3.06%</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>138→159</t>
+        </is>
+      </c>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="H61" s="15" t="n">
+        <v>-27</v>
+      </c>
+      <c r="I61" s="15" t="n">
+        <v>-49145400</v>
+      </c>
+      <c r="J61" s="16" t="inlineStr">
+        <is>
+          <t>6.43%→6.27%</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="inlineStr">
+        <is>
+          <t>1,020→993</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C62" s="11" t="n">
+        <v>39314800</v>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>7.27%→7.42%</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>747→761</t>
+        </is>
+      </c>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>원익머트리얼즈</t>
+        </is>
+      </c>
+      <c r="H62" s="15" t="n">
+        <v>-18</v>
+      </c>
+      <c r="I62" s="15" t="n">
+        <v>-50000400</v>
+      </c>
+      <c r="J62" s="16" t="inlineStr">
+        <is>
+          <t>2.59%→2.42%</t>
+        </is>
+      </c>
+      <c r="K62" s="13" t="inlineStr">
+        <is>
+          <t>269→251</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C63" s="11" t="n">
+        <v>74350800</v>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>2.06%→2.32%</t>
+        </is>
+      </c>
+      <c r="E63" s="13" t="inlineStr">
+        <is>
+          <t>72→81</t>
+        </is>
+      </c>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="H63" s="15" t="n">
+        <v>-14</v>
+      </c>
+      <c r="I63" s="15" t="n">
+        <v>-32877600</v>
+      </c>
+      <c r="J63" s="16" t="inlineStr">
+        <is>
+          <t>2.61%→2.50%</t>
+        </is>
+      </c>
+      <c r="K63" s="13" t="inlineStr">
+        <is>
+          <t>321→307</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C64" s="11" t="n">
+        <v>46648800</v>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>3.29%→3.45%</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <t>183→192</t>
+        </is>
+      </c>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>솔브레인홀딩스</t>
+        </is>
+      </c>
+      <c r="H64" s="15" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I64" s="15" t="n">
+        <v>-39470600</v>
+      </c>
+      <c r="J64" s="16" t="inlineStr">
+        <is>
+          <t>0.73%→0.59%</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="inlineStr">
+        <is>
+          <t>69→56</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C65" s="11" t="n">
+        <v>61149600</v>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>2.90%→3.11%</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>82→88</t>
+        </is>
+      </c>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>티씨케이</t>
+        </is>
+      </c>
+      <c r="H65" s="15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I65" s="15" t="n">
+        <v>-166896000</v>
+      </c>
+      <c r="J65" s="16" t="inlineStr">
+        <is>
+          <t>2.83%→2.25%</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="inlineStr">
+        <is>
+          <t>44→35</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
           <t>실리콘투</t>
         </is>
       </c>
-      <c r="B40" s="11" t="n">
+      <c r="B66" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C40" s="11" t="n">
+      <c r="C66" s="11" t="n">
         <v>13026400</v>
       </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="D66" s="12" t="inlineStr">
         <is>
           <t>0.82%→0.87%</t>
         </is>
       </c>
-      <c r="E40" s="13" t="inlineStr">
+      <c r="E66" s="13" t="inlineStr">
         <is>
           <t>73→77</t>
         </is>
       </c>
-      <c r="G40" s="14" t="inlineStr">
+      <c r="G66" s="14" t="inlineStr">
         <is>
           <t>클래시스</t>
         </is>
       </c>
-      <c r="H40" s="15" t="n">
+      <c r="H66" s="15" t="n">
         <v>-8</v>
       </c>
-      <c r="I40" s="15" t="n">
+      <c r="I66" s="15" t="n">
         <v>-22800000</v>
       </c>
-      <c r="J40" s="16" t="inlineStr">
+      <c r="J66" s="16" t="inlineStr">
         <is>
           <t>0.55%→0.47%</t>
         </is>
       </c>
-      <c r="K40" s="13" t="inlineStr">
+      <c r="K66" s="13" t="inlineStr">
         <is>
           <t>56→48</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="19" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 586억   ·   현금 20억(3.3%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n"/>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="4" t="n"/>
-      <c r="E42" s="4" t="n"/>
-      <c r="F42" s="4" t="n"/>
-      <c r="G42" s="4" t="n"/>
-      <c r="H42" s="4" t="n"/>
-      <c r="I42" s="4" t="n"/>
-      <c r="J42" s="4" t="n"/>
-      <c r="K42" s="4" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t>변화 없음 (구성종목 동일)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="19" customHeight="1">
-      <c r="A45" s="18" t="inlineStr">
+    <row r="68" ht="19" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 586억   ·   현금 9억(1.5%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 1종목  /  매도 1종목</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="n"/>
+      <c r="C68" s="4" t="n"/>
+      <c r="D68" s="4" t="n"/>
+      <c r="E68" s="4" t="n"/>
+      <c r="F68" s="4" t="n"/>
+      <c r="G68" s="4" t="n"/>
+      <c r="H68" s="4" t="n"/>
+      <c r="I68" s="4" t="n"/>
+      <c r="J68" s="4" t="n"/>
+      <c r="K68" s="4" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="n"/>
+      <c r="C69" s="6" t="n"/>
+      <c r="D69" s="6" t="n"/>
+      <c r="E69" s="6" t="n"/>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="n"/>
+      <c r="I69" s="8" t="n"/>
+      <c r="J69" s="8" t="n"/>
+      <c r="K69" s="8" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K70" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>인제니아테라퓨틱스(Reg.S)  (신규)</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="n">
+        <v>655</v>
+      </c>
+      <c r="C71" s="11" t="n">
+        <v>1425797450</v>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→2.52%</t>
+        </is>
+      </c>
+      <c r="E71" s="13" t="inlineStr">
+        <is>
+          <t>0→655</t>
+        </is>
+      </c>
+      <c r="G71" s="14" t="inlineStr">
+        <is>
+          <t>한스바이오메드</t>
+        </is>
+      </c>
+      <c r="H71" s="15" t="n">
+        <v>-210</v>
+      </c>
+      <c r="I71" s="15" t="n">
+        <v>-522175500</v>
+      </c>
+      <c r="J71" s="16" t="inlineStr">
+        <is>
+          <t>2.79%→1.77%</t>
+        </is>
+      </c>
+      <c r="K71" s="13" t="inlineStr">
+        <is>
+          <t>612→402</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="19" customHeight="1">
+      <c r="A73" s="18" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B45" s="19" t="n"/>
-      <c r="C45" s="19" t="n"/>
-      <c r="D45" s="19" t="n"/>
-      <c r="E45" s="19" t="n"/>
-      <c r="F45" s="19" t="n"/>
-      <c r="G45" s="19" t="n"/>
-      <c r="H45" s="19" t="n"/>
-      <c r="I45" s="19" t="n"/>
-      <c r="J45" s="19" t="n"/>
-      <c r="K45" s="19" t="n"/>
+      <c r="B73" s="19" t="n"/>
+      <c r="C73" s="19" t="n"/>
+      <c r="D73" s="19" t="n"/>
+      <c r="E73" s="19" t="n"/>
+      <c r="F73" s="19" t="n"/>
+      <c r="G73" s="19" t="n"/>
+      <c r="H73" s="19" t="n"/>
+      <c r="I73" s="19" t="n"/>
+      <c r="J73" s="19" t="n"/>
+      <c r="K73" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A22:K22"/>
-    <mergeCell ref="A29:E29"/>
+  <mergeCells count="21">
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="A73:K73"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A54:K54"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A46:K46"/>
+    <mergeCell ref="G69:K69"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="G55:K55"/>
+    <mergeCell ref="G4:K4"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="G29:K29"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A21:K21"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="A43:K43"/>
-    <mergeCell ref="A24:K24"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A45:K45"/>
-    <mergeCell ref="A28:K28"/>
-    <mergeCell ref="A42:K42"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="G47:K47"/>
+    <mergeCell ref="G25:K25"/>
+    <mergeCell ref="A68:K68"/>
+    <mergeCell ref="G31:K31"/>
+    <mergeCell ref="A31:E31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260819.xlsx
+++ b/reports/pdf_rolling5_20260819.xlsx
@@ -1985,23 +1985,23 @@
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>케어젠  (편출)</t>
         </is>
       </c>
       <c r="H40" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-204483600</v>
+        <v>-1207920000</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>0.36%→0.25%</t>
+          <t>0.45%→0.00%</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
-          <t>101→77</t>
+          <t>24→0</t>
         </is>
       </c>
     </row>
@@ -2013,23 +2013,23 @@
       <c r="E41" s="17" t="n"/>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>케어젠  (편출)</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-1207920000</v>
+        <v>-204483600</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>0.45%→0.00%</t>
+          <t>0.36%→0.25%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>24→0</t>
+          <t>101→77</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260819.xlsx
+++ b/reports/pdf_rolling5_20260819.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,778억   ·   현금 273억(5.7%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 17종목  /  매도 17종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,674억   ·   현금 272억(5.7%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 17종목  /  매도 17종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,7 +665,7 @@
         <v>244</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2707794880</v>
+        <v>2702602560</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         <v>-337</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-3465701260</v>
+        <v>-3459055620</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>126</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1389088260</v>
+        <v>1386424620</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>-62</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-962230080</v>
+        <v>-960384960</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>113</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>460828690</v>
+        <v>459945030</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>-36</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-929313000</v>
+        <v>-927531000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>69</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>4066135500</v>
+        <v>4058338500</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>-35</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-2493291500</v>
+        <v>-2488510500</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>67</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>861632730</v>
+        <v>859980510</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>-33</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-3817067100</v>
+        <v>-3809747700</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>49</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1323671300</v>
+        <v>1321133100</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>-33</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1349224800</v>
+        <v>-1346637600</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>39</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>929469450</v>
+        <v>927687150</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>-29</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-916484100</v>
+        <v>-914726700</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>29</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1845067000</v>
+        <v>1841529000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>-27</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-2247247800</v>
+        <v>-2242938600</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>27</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>3041388000</v>
+        <v>3035556000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>-26</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-455582400</v>
+        <v>-454708800</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>24</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>963732000</v>
+        <v>961884000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>-25</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-2912577500</v>
+        <v>-2906992500</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>18</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>462779100</v>
+        <v>461891700</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>-24</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-927435600</v>
+        <v>-925657200</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>17</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>955700900</v>
+        <v>953868300</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>-20</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-713412000</v>
+        <v>-712044000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>11</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>902925100</v>
+        <v>901193700</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>-19</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-1722097300</v>
+        <v>-1718795100</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>9</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>458554950</v>
+        <v>457675650</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>-15</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-904281000</v>
+        <v>-902547000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>8</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>2244536000</v>
+        <v>2240232000</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>-8</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-876954400</v>
+        <v>-875272800</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>7</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>2175698000</v>
+        <v>2171526000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>-7</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-486246600</v>
+        <v>-485314200</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>5</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>395297000</v>
+        <v>394539000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>-3</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-1229697000</v>
+        <v>-1227339000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,023억   ·   현금 11억(0.3%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 1종목  /  매도 2종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,837억   ·   현금 11억(0.3%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 1종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1502,7 +1502,7 @@
         <v>424</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>4027457280</v>
+        <v>4042712800</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>-123</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-1457992800</v>
+        <v>-1463515500</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>-5</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-321552000</v>
+        <v>-322770000</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,774억   ·   현금 81억(3.0%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 8종목  /  매도 12종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,691억   ·   현금 81억(3.0%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 8종목  /  매도 12종목</t>
         </is>
       </c>
       <c r="B30" s="4" t="n"/>
@@ -1663,7 +1663,7 @@
         <v>116</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>804848600</v>
+        <v>800371000</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>-275</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-1949568500</v>
+        <v>-1938722500</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>94</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>1090162180</v>
+        <v>1084097300</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>-171</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-2104886880</v>
+        <v>-2093176800</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>69</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>5357988000</v>
+        <v>5328180000</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>-145</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-3779243750</v>
+        <v>-3758218750</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>68</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>3706013600</v>
+        <v>3685396000</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>-130</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-1739476700</v>
+        <v>-1729799500</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>47</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>587998200</v>
+        <v>584727000</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>-119</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-2939020350</v>
+        <v>-2922669750</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>33</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>1447347000</v>
+        <v>1439295000</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>-70</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-1245667500</v>
+        <v>-1238737500</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>15</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>2901165000</v>
+        <v>2885025000</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>-34</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-1317639400</v>
+        <v>-1310309000</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>14</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>2808414000</v>
+        <v>2792790000</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>-24</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-1207920000</v>
+        <v>-1201200000</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>-24</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-204483600</v>
+        <v>-203346000</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>-23</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-1847182900</v>
+        <v>-1836906500</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>-20</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-957708000</v>
+        <v>-952380000</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>-18</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-2320500600</v>
+        <v>-2307591000</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,346억   ·   현금 50억(2.2%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 4종목  /  매도 4종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,234억   ·   현금 50억(2.2%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B46" s="4" t="n"/>
@@ -2216,7 +2216,7 @@
         <v>233</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>3309555300</v>
+        <v>3319318000</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>-216</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-1163529360</v>
+        <v>-1166961600</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>154</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>10206273000</v>
+        <v>10236380000</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>-120</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-12122640000</v>
+        <v>-12158400000</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>84</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>2266689600</v>
+        <v>2273376000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>-62</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-2238417000</v>
+        <v>-2245020000</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>4</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>30645600</v>
+        <v>30736000</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>-53</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-1180431900</v>
+        <v>-1183914000</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
     <row r="54" ht="19" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 295억   ·   현금 15억(4.8%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 10종목  /  매도 10종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 288억   ·   현금 15억(4.9%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 10종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B54" s="4" t="n"/>
@@ -2481,11 +2481,11 @@
         <v>105</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>75810000</v>
+        <v>66872400</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>0.04%→0.31%</t>
+          <t>0.04%→0.28%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -2502,11 +2502,11 @@
         <v>-194</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-137414080</v>
+        <v>-131074160</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>7.97%→7.50%</t>
+          <t>7.79%→7.34%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
@@ -2525,11 +2525,11 @@
         <v>74</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>68894000</v>
+        <v>64563520</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>1.43%→1.67%</t>
+          <t>1.37%→1.60%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
@@ -2546,11 +2546,11 @@
         <v>-43</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-36732320</v>
+        <v>-35032960</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>2.81%→2.69%</t>
+          <t>2.75%→2.63%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
@@ -2569,11 +2569,11 @@
         <v>34</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>48605040</v>
+        <v>47080480</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>3.20%→3.37%</t>
+          <t>3.18%→3.35%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
@@ -2590,11 +2590,11 @@
         <v>-38</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-52792640</v>
+        <v>-52215040</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>1.55%→1.37%</t>
+          <t>1.57%→1.39%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
@@ -2613,11 +2613,11 @@
         <v>29</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>32090240</v>
+        <v>26470040</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>0.08%→0.20%</t>
+          <t>0.07%→0.17%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
@@ -2634,11 +2634,11 @@
         <v>-30</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-60306000</v>
+        <v>-58710000</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>2.77%→2.56%</t>
+          <t>2.76%→2.56%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
@@ -2657,11 +2657,11 @@
         <v>21</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>116348400</v>
+        <v>106293600</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>2.65%→3.06%</t>
+          <t>2.48%→2.86%</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
@@ -2678,11 +2678,11 @@
         <v>-27</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-49145400</v>
+        <v>-46067400</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>6.43%→6.27%</t>
+          <t>6.18%→6.03%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
@@ -2701,11 +2701,11 @@
         <v>14</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>39314800</v>
+        <v>39421200</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>7.27%→7.42%</t>
+          <t>7.47%→7.62%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
@@ -2722,11 +2722,11 @@
         <v>-18</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-50000400</v>
+        <v>-49111200</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>2.59%→2.42%</t>
+          <t>2.61%→2.44%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
@@ -2745,11 +2745,11 @@
         <v>9</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>74350800</v>
+        <v>75855600</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>2.06%→2.32%</t>
+          <t>2.16%→2.43%</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
@@ -2766,11 +2766,11 @@
         <v>-14</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-32877600</v>
+        <v>-38570000</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>2.61%→2.50%</t>
+          <t>3.14%→3.01%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
@@ -2789,11 +2789,11 @@
         <v>9</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>46648800</v>
+        <v>45622800</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>3.29%→3.45%</t>
+          <t>3.29%→3.46%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
@@ -2810,7 +2810,7 @@
         <v>-13</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-39470600</v>
+        <v>-38680200</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
@@ -2833,11 +2833,11 @@
         <v>6</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>61149600</v>
+        <v>60192000</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>2.90%→3.11%</t>
+          <t>2.92%→3.14%</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
@@ -2854,11 +2854,11 @@
         <v>-9</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-166896000</v>
+        <v>-158688000</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>2.83%→2.25%</t>
+          <t>2.76%→2.20%</t>
         </is>
       </c>
       <c r="K65" s="13" t="inlineStr">
@@ -2877,11 +2877,11 @@
         <v>4</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>13026400</v>
+        <v>13528000</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>0.82%→0.87%</t>
+          <t>0.88%→0.93%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
@@ -2898,11 +2898,11 @@
         <v>-8</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-22800000</v>
+        <v>-21097600</v>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
-          <t>0.55%→0.47%</t>
+          <t>0.52%→0.45%</t>
         </is>
       </c>
       <c r="K66" s="13" t="inlineStr">
@@ -2914,7 +2914,7 @@
     <row r="68" ht="19" customHeight="1">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 586억   ·   현금 9억(1.5%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 1종목  /  매도 1종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 555억   ·   현금 8억(1.5%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 1종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B68" s="4" t="n"/>
@@ -3010,7 +3010,7 @@
         <v>655</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>1425797450</v>
+        <v>1402230550</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>-210</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-522175500</v>
+        <v>-513544500</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>

--- a/reports/pdf_rolling5_20260819.xlsx
+++ b/reports/pdf_rolling5_20260819.xlsx
@@ -855,23 +855,23 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-33</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-3809747700</v>
+        <v>-1346637600</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>5.65%→4.68%</t>
+          <t>1.50%→1.48%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>217→184</t>
+          <t>198→165</t>
         </is>
       </c>
     </row>
@@ -899,23 +899,23 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-33</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1346637600</v>
+        <v>-3809747700</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>1.50%→1.48%</t>
+          <t>5.65%→4.68%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>198→165</t>
+          <t>217→184</t>
         </is>
       </c>
     </row>
@@ -1985,23 +1985,23 @@
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>케어젠  (편출)</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="H40" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-1201200000</v>
+        <v>-203346000</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>0.45%→0.00%</t>
+          <t>0.36%→0.25%</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
-          <t>24→0</t>
+          <t>101→77</t>
         </is>
       </c>
     </row>
@@ -2013,23 +2013,23 @@
       <c r="E41" s="17" t="n"/>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>케어젠  (편출)</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-203346000</v>
+        <v>-1201200000</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>0.36%→0.25%</t>
+          <t>0.45%→0.00%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>101→77</t>
+          <t>24→0</t>
         </is>
       </c>
     </row>
@@ -2738,23 +2738,23 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B63" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>75855600</v>
+        <v>45622800</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>2.16%→2.43%</t>
+          <t>3.29%→3.46%</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>72→81</t>
+          <t>183→192</t>
         </is>
       </c>
       <c r="G63" s="14" t="inlineStr">
@@ -2782,23 +2782,23 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B64" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>45622800</v>
+        <v>75855600</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>3.29%→3.46%</t>
+          <t>2.16%→2.43%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>183→192</t>
+          <t>72→81</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260819.xlsx
+++ b/reports/pdf_rolling5_20260819.xlsx
@@ -2738,23 +2738,23 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B63" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>45622800</v>
+        <v>75855600</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>3.29%→3.46%</t>
+          <t>2.16%→2.43%</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>183→192</t>
+          <t>72→81</t>
         </is>
       </c>
       <c r="G63" s="14" t="inlineStr">
@@ -2782,23 +2782,23 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B64" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>75855600</v>
+        <v>45622800</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>2.16%→2.43%</t>
+          <t>3.29%→3.46%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>72→81</t>
+          <t>183→192</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260819.xlsx
+++ b/reports/pdf_rolling5_20260819.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,674억   ·   현금 272억(5.7%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 17종목  /  매도 17종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,674억   ·   현금 136억(2.9%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 17종목  /  매도 17종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -1406,7 +1406,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,837억   ·   현금 11억(0.3%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 1종목  /  매도 2종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,837억   ·   현금 6억(0.1%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 1종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1567,7 +1567,7 @@
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,691억   ·   현금 81억(3.0%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 8종목  /  매도 12종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,691억   ·   현금 40억(1.5%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 8종목  /  매도 12종목</t>
         </is>
       </c>
       <c r="B30" s="4" t="n"/>
@@ -1985,23 +1985,23 @@
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>케어젠  (편출)</t>
         </is>
       </c>
       <c r="H40" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-203346000</v>
+        <v>-1201200000</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>0.36%→0.25%</t>
+          <t>0.45%→0.00%</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
-          <t>101→77</t>
+          <t>24→0</t>
         </is>
       </c>
     </row>
@@ -2013,23 +2013,23 @@
       <c r="E41" s="17" t="n"/>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>케어젠  (편출)</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-1201200000</v>
+        <v>-203346000</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>0.45%→0.00%</t>
+          <t>0.36%→0.25%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>24→0</t>
+          <t>101→77</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,234억   ·   현금 50억(2.2%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 4종목  /  매도 4종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,234억   ·   현금 25억(1.1%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B46" s="4" t="n"/>
@@ -2385,7 +2385,7 @@
     <row r="54" ht="19" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 288억   ·   현금 15억(4.9%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 10종목  /  매도 10종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 288억   ·   현금 7억(2.5%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 10종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B54" s="4" t="n"/>
@@ -2738,23 +2738,23 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B63" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>75855600</v>
+        <v>45622800</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>2.16%→2.43%</t>
+          <t>3.29%→3.46%</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>72→81</t>
+          <t>183→192</t>
         </is>
       </c>
       <c r="G63" s="14" t="inlineStr">
@@ -2782,23 +2782,23 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B64" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>45622800</v>
+        <v>75855600</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>3.29%→3.46%</t>
+          <t>2.16%→2.43%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>183→192</t>
+          <t>72→81</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -2914,7 +2914,7 @@
     <row r="68" ht="19" customHeight="1">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 555억   ·   현금 8억(1.5%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 1종목  /  매도 1종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 555억   ·   현금 4억(0.8%)      오늘 2026-08-19  vs  5일전 2026-08-11      매수 1종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B68" s="4" t="n"/>
